--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487958_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487958_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8229</v>
+        <v>4.5869</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0705</v>
+        <v>4.0311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7524</v>
+        <v>0.5558</v>
       </c>
       <c r="G2" t="n">
         <v>3.4012</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2323</v>
+        <v>-0.0037</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0989</v>
+        <v>-0.1384</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3313</v>
+        <v>0.1347</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7151</v>
+        <v>3.3596</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1919</v>
+        <v>0.9487</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5232</v>
+        <v>2.4109</v>
       </c>
       <c r="G3" t="n">
         <v>4.8766</v>
@@ -688,13 +688,13 @@
         <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8207</v>
+        <v>0.4652</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0072</v>
+        <v>-0.2505</v>
       </c>
       <c r="U3" t="n">
-        <v>0.828</v>
+        <v>0.7157</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7163</v>
+        <v>1.891</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.082</v>
+        <v>-0.0196</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7984</v>
+        <v>1.9107</v>
       </c>
       <c r="G4" t="n">
         <v>2.5541</v>
@@ -766,13 +766,13 @@
         <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3729</v>
+        <v>-0.1982</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4881</v>
+        <v>-0.4257</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1152</v>
+        <v>0.2275</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8506</v>
+        <v>1.1439</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1406</v>
+        <v>1.2654</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.29</v>
+        <v>-0.1215</v>
       </c>
       <c r="G5" t="n">
         <v>1.8241</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4493</v>
+        <v>-0.156</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5357</v>
+        <v>-0.4109</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.2549</v>
       </c>
       <c r="V5" t="n">
         <v>0.0704</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.327</v>
+        <v>0.6421</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4568</v>
+        <v>-1.3944</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7838</v>
+        <v>2.0365</v>
       </c>
       <c r="G6" t="n">
         <v>1.4132</v>
@@ -922,13 +922,13 @@
         <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3528</v>
+        <v>-0.0377</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2496</v>
+        <v>-0.1872</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1032</v>
+        <v>0.1495</v>
       </c>
       <c r="V6" t="n">
         <v>-0.337</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GUERRERO JONSSON</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0271</v>
+        <v>0.155</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0202</v>
+        <v>-0.1451</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0472</v>
+        <v>0.3001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0458</v>
+        <v>0.0012</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0458</v>
+        <v>-0.2608</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.2621</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0202</v>
+        <v>0.1274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>0.0069</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.066</v>
+        <v>-0.1262</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.066</v>
+        <v>-0.2677</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1415</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0187</v>
+        <v>-0.1744</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2725</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0187</v>
+        <v>0.0982</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>D. GUERRERO JONSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0873</v>
+        <v>0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2469</v>
+        <v>0.0202</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1597</v>
+        <v>-0.0192</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0012</v>
+        <v>-0.0458</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2608</v>
+        <v>-0.0458</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2621</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1274</v>
+        <v>0.0202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0069</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1262</v>
+        <v>-0.066</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2677</v>
+        <v>-0.066</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1415</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4166</v>
+        <v>0.0468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3744</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0422</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4781</v>
+        <v>-0.7246</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7483</v>
+        <v>-1.9111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2702</v>
+        <v>1.1865</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0069</v>
+        <v>2.0498</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2441</v>
+        <v>1.2387</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2372</v>
+        <v>0.8111</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8558</v>
+        <v>0.8002</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9685</v>
+        <v>1.3588</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1128</v>
+        <v>-0.5586</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1512</v>
+        <v>1.2495</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2756</v>
+        <v>-0.1201</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1244</v>
+        <v>1.3697</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1097</v>
+        <v>-0.0827</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3782</v>
+        <v>-0.5111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7315</v>
+        <v>0.4284</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>-3.0882</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-1.0109</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7995</v>
+        <v>-0.8504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6484</v>
+        <v>-1.7273</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8489</v>
+        <v>0.877</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2308</v>
@@ -1234,13 +1234,13 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.095</v>
+        <v>-0.1459</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0586</v>
+        <v>-0.1376</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0364</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.204</v>
+        <v>-0.9573</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1378</v>
+        <v>-1.031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9338</v>
+        <v>0.0737</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0498</v>
+        <v>1.0069</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2387</v>
+        <v>1.2441</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8111</v>
+        <v>-0.2372</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8002</v>
+        <v>0.8558</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3588</v>
+        <v>0.9685</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5586</v>
+        <v>-0.1128</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2495</v>
+        <v>0.1512</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1201</v>
+        <v>0.2756</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3697</v>
+        <v>-0.1244</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.6304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7377</v>
+        <v>0.0955</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1757</v>
+        <v>0.5349</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0882</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.0109</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0772</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9586</v>
+        <v>-1.8038</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5412</v>
+        <v>-2.1337</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5827</v>
+        <v>0.3299</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6279</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3484</v>
+        <v>-0.1937</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7781</v>
+        <v>-0.3706</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4296</v>
+        <v>0.1769</v>
       </c>
       <c r="V12" t="n">
         <v>3.0178</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.176</v>
+        <v>-1.806</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3902</v>
+        <v>-3.7955</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2142</v>
+        <v>1.9896</v>
       </c>
       <c r="G13" t="n">
         <v>1.2459</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3187</v>
+        <v>0.0514</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.3816</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6576</v>
+        <v>0.433</v>
       </c>
       <c r="V13" t="n">
         <v>0.2666</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.701300000000001</v>
+        <v>5.6374</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.8284</v>
+        <v>-5.892300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>11.5301</v>
+        <v>11.53</v>
       </c>
       <c r="G14" t="n">
         <v>12.4685</v>
@@ -1546,16 +1546,16 @@
         <v>11.8935</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7343000000000004</v>
+        <v>0.2015</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9264</v>
+        <v>-2.9906</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1923</v>
+        <v>3.1921</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0773</v>
+        <v>-2.077300000000001</v>
       </c>
       <c r="W14" t="n">
         <v>2.8066</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8682</v>
+        <v>3.262</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2336</v>
+        <v>1.6411</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6346</v>
+        <v>1.6209</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1289</v>
@@ -1624,13 +1624,13 @@
         <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4459</v>
+        <v>0.8397</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6936</v>
+        <v>-0.2861</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1395</v>
+        <v>1.1258</v>
       </c>
       <c r="V15" t="n">
         <v>2.5601</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5565</v>
+        <v>1.2685</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2723</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2842</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
         <v>0.0583</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1017</v>
+        <v>-0.1862</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2568</v>
+        <v>-0.4606</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3586</v>
+        <v>0.2743</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1402</v>
+        <v>1.0514</v>
       </c>
       <c r="E17" t="n">
         <v>1.6132</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4729</v>
+        <v>-0.5617</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0105</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2981</v>
+        <v>0.2093</v>
       </c>
       <c r="T17" t="n">
         <v>-0.6936</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9917</v>
+        <v>0.9029</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3278</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4684</v>
+        <v>0.74</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9532</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4215</v>
+        <v>1.6932</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9192</v>
@@ -1936,13 +1936,13 @@
         <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1982</v>
+        <v>0.4699</v>
       </c>
       <c r="T19" t="n">
         <v>0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1431</v>
+        <v>0.4147</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3027</v>
+        <v>0.4372</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3027</v>
+        <v>-2.0605</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.4978</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3027</v>
+        <v>-2.823</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3027</v>
+        <v>1.5045</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-4.3275</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3027</v>
+        <v>-1.9959</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3027</v>
+        <v>1.2792</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-3.2751</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.2253</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-1.0524</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3194</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.2806</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1568</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.0503</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1118</v>
+        <v>0.3027</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2716</v>
+        <v>0.3027</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3834</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9668</v>
+        <v>0.3027</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4291</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5376</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6388</v>
+        <v>0.3027</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0404</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.328</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4695</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1415</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,28 +2092,28 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7415</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3671</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3744</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0473</v>
+        <v>-0.2957</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8568</v>
+        <v>-0.6791</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8095</v>
+        <v>0.3834</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.823</v>
+        <v>-0.9668</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5045</v>
+        <v>-0.4291</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3275</v>
+        <v>-0.5376</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9959</v>
+        <v>-0.6388</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2792</v>
+        <v>0.0404</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.2751</v>
+        <v>-0.6791</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.328</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2253</v>
+        <v>-0.4695</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0524</v>
+        <v>0.1415</v>
       </c>
       <c r="P22" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1651</v>
+        <v>0.334</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0769</v>
+        <v>-0.0403</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0883</v>
+        <v>0.3744</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1568</v>
+        <v>0.337</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0503</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. MARKOTA</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4927</v>
+        <v>-0.3044</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3601</v>
+        <v>-1.0948</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.7905</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3243</v>
+        <v>1.4042</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2081</v>
+        <v>1.5133</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5325</v>
+        <v>-0.1091</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2085</v>
+        <v>3.1065</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0694</v>
+        <v>1.8973</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2779</v>
+        <v>1.2092</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1158</v>
+        <v>-1.7023</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8613</v>
+        <v>-0.3839</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2545</v>
+        <v>-1.3184</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4967</v>
+        <v>0.3964</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2975</v>
+        <v>-0.433</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1992</v>
+        <v>0.8294</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5331</v>
+        <v>0.0755</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5331</v>
+        <v>0.1962</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>P. MARKOTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5268</v>
+        <v>-0.4424</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9098</v>
+        <v>-1.6657</v>
       </c>
       <c r="F24" t="n">
-        <v>0.383</v>
+        <v>1.2233</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4042</v>
+        <v>-1.3243</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5133</v>
+        <v>0.2081</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1091</v>
+        <v>-1.5325</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1065</v>
+        <v>-0.2085</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8973</v>
+        <v>1.0694</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2092</v>
+        <v>-1.2779</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7023</v>
+        <v>-1.1158</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3839</v>
+        <v>-0.8613</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3184</v>
+        <v>-0.2545</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
         <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.826</v>
+        <v>0.547</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2479</v>
+        <v>-0.0081</v>
       </c>
       <c r="U24" t="n">
-        <v>0.422</v>
+        <v>0.5551</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0755</v>
+        <v>0.5331</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1962</v>
+        <v>0.5331</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8747</v>
+        <v>-1.8185</v>
       </c>
       <c r="E25" t="n">
         <v>-1.8373</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0374</v>
+        <v>0.0188</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3285</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1498</v>
+        <v>-0.0936</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.563</v>
+        <v>-2.2646</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6877</v>
+        <v>-2.5858</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1247</v>
+        <v>0.3212</v>
       </c>
       <c r="G26" t="n">
         <v>-2.059</v>
@@ -2482,13 +2482,13 @@
         <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.504</v>
+        <v>-0.2055</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4992</v>
+        <v>-0.3973</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0048</v>
+        <v>0.1918</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.5501</v>
+        <v>-5.5057</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.9806</v>
+        <v>-5.1843</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5695</v>
+        <v>-0.3214</v>
       </c>
       <c r="G27" t="n">
         <v>-4.579</v>
@@ -2560,13 +2560,13 @@
         <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0969</v>
+        <v>0.1413</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2568</v>
+        <v>-0.4606</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3538</v>
+        <v>0.6019</v>
       </c>
       <c r="V27" t="n">
         <v>-1.861</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.701499999999999</v>
+        <v>-2.664200000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.53</v>
+        <v>-11.5299</v>
       </c>
       <c r="F28" t="n">
-        <v>6.8285</v>
+        <v>8.866</v>
       </c>
       <c r="G28" t="n">
         <v>-12.4687</v>
@@ -2611,7 +2611,7 @@
         <v>-11.4595</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.327999999999999</v>
+        <v>-1.328</v>
       </c>
       <c r="K28" t="n">
         <v>3.5686</v>
@@ -2638,13 +2638,13 @@
         <v>16.8489</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7341</v>
+        <v>2.7717</v>
       </c>
       <c r="T28" t="n">
         <v>-3.1922</v>
       </c>
       <c r="U28" t="n">
-        <v>3.9266</v>
+        <v>5.9639</v>
       </c>
       <c r="V28" t="n">
         <v>2.0773</v>
